--- a/kb/医学知识库源数据.xlsx
+++ b/kb/医学知识库源数据.xlsx
@@ -479,12 +479,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>聚焦科室</t>
+          <t>覆盖科室</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>消化内科/心血管内科/呼吸内科/神经内科/急诊科 5 个高频科室</t>
+          <t>14 个科室全覆盖，其中消化/心血管/呼吸/神经/内分泌等做深</t>
         </is>
       </c>
     </row>
@@ -559,13 +559,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
@@ -611,7 +611,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>腹痛|腹泻|恶心|呕吐|反酸|烧心|便血|黑便</t>
+          <t>腹痛|腹泻|恶心|呕吐|反酸|烧心|便血|黑便|腹胀</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>胸痛|胸闷|心悸|心慌|气短|高血压</t>
+          <t>胸痛|胸闷|心悸|心慌|气短|高血压|心前区痛</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -692,7 +692,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>头痛|头晕|眩晕|肢体无力|麻木|抽搐|面瘫</t>
+          <t>头痛|头晕|眩晕|肢体无力|麻木|抽搐|面瘫|言语不清</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -719,34 +719,34 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>剧烈胸痛|大出血|昏迷|休克|严重外伤</t>
+          <t>多饮|多尿|体重下降|怕冷|多汗|消瘦|关节红肿</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>EMER</t>
+          <t>END</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>急诊科</t>
+          <t>内分泌科</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>红旗症状直接急诊（高优先级）</t>
+          <t>内分泌代谢症状</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>尿频|尿急|尿痛|血尿|腰痛</t>
+          <t>尿频|尿急|尿痛|血尿|排尿困难|肾绞痛</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -766,14 +766,14 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>泌尿症状</t>
+          <t>泌尿系统症状</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>下腹痛|月经不调|痛经|白带异常|阴道出血</t>
+          <t>白带异常|月经不调|痛经|下腹痛|阴道出血</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>停经|早孕|孕期腹痛|胎动异常</t>
+          <t>停经|早孕|孕期腹痛|胎动异常|孕期出血</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>骨折|关节痛|腰背痛|扭伤</t>
+          <t>腰痛|腰背痛|关节痛|颈痛|骨折|扭伤|活动受限</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -855,14 +855,14 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>骨关节症状</t>
+          <t>骨关节与运动系统症状</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>皮疹|瘙痒|红肿|脱发|湿疹</t>
+          <t>皮疹|瘙痒|风团|水疱|脱发|红斑</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>咽痛|鼻塞|流涕|耳鸣|听力下降|声音嘶哑</t>
+          <t>咽痛|鼻塞|流涕|耳鸣|耳痛|听力下降|声音嘶哑</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -916,7 +916,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>眼红|眼痛|视力下降|视物模糊</t>
+          <t>眼红|眼痛|视力下降|视物模糊|眼干|流泪</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -943,7 +943,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>失眠|焦虑|抑郁|情绪低落|恐慌</t>
+          <t>失眠|焦虑|抑郁|情绪低落|恐慌|坐立不安</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -964,6 +964,450 @@
       <c r="G14" s="3" t="inlineStr">
         <is>
           <t>精神心理症状</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>剧烈胸痛|昏迷|休克|抽搐|大出血|严重外伤|意识障碍</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>EMER</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>急诊科</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>红旗症状直接急诊（最高优先级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>呕吐伴腹泻|腹痛伴发热</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>DIG</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>消化内科</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>消化系统感染表现</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>咳嗽伴气短|喘息发作</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>呼吸内科</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>下呼吸道症状</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>头痛伴头晕|肢体麻木</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>神经内科</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>神经系统复合症状</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>尿痛伴发热</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>URO</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>泌尿外科</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>泌尿系感染可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>下腹痛伴白带异常</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>GYN</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>妇科</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>妇科炎症可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>关节痛伴红肿</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>ORTH</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>骨科</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>关节炎症可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>皮疹伴瘙痒</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>DERM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>皮肤科</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>皮肤过敏可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>咽痛伴发热</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>ENT</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>耳鼻喉科</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>上呼吸道感染可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>视物模糊伴眼痛</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>OPH</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>眼部急症可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>心悸伴多汗消瘦</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>内分泌科</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>甲状腺功能异常可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>夜间胸痛|餐后反酸</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>DIG</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>消化内科</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>胃食管反流可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>活动后气短</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>心血管内科</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>心功能评估</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>发热伴皮疹</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>DERM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>皮肤科</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>感染性皮疹可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>儿童发热|儿童腹泻</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>呼吸内科</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>儿童常见感染</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>老年人头晕|老年人乏力</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>神经内科</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>elderly</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>老年神经系统评估</t>
         </is>
       </c>
     </row>
@@ -978,12 +1422,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1092,17 +1536,17 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>胸痛</t>
+          <t>腹泻</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>frequency</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>胸痛是什么样的（压榨、针刺、烧灼）？</t>
+          <t>一天腹泻几次？大便是什么样子（水样、糊状、带血）？</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1112,17 +1556,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>胸痛</t>
+          <t>腹泻</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有放射到左臂、下颌或后背？</t>
+          <t>腹泻多久了？</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1132,17 +1576,17 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>胸痛</t>
+          <t>腹泻</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>什么情况下会加重（活动、劳累、深呼吸）？</t>
+          <t>有没有腹痛、发热、呕吐、脱水表现？</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1152,17 +1596,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>头痛</t>
+          <t>胸痛</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>头痛在哪个部位（太阳穴、后脑勺、全头）？</t>
+          <t>胸痛是什么样的（压榨、针刺、烧灼）？</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1172,17 +1616,17 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>头痛</t>
+          <t>胸痛</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>radiation</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>是胀痛、跳痛还是刺痛？</t>
+          <t>疼痛有没有放射到左臂、下颌或后背？</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1192,17 +1636,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>头痛</t>
+          <t>胸痛</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>有没有恶心、呕吐、畏光、发热？</t>
+          <t>什么情况下会加重（活动、劳累、深呼吸）？</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1212,17 +1656,17 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>咳嗽</t>
+          <t>胸闷</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>咳嗽多久了？</t>
+          <t>胸闷在什么情况下出现（活动、休息、夜间）？</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1232,17 +1676,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>咳嗽</t>
+          <t>胸闷</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>sputum</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>有没有痰？痰是什么颜色？</t>
+          <t>每次持续多久？能否自行缓解？</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1252,117 +1696,117 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>咳嗽</t>
+          <t>心悸</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>心慌在什么情况下出现？持续多久？</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>发热</t>
+          <t>心悸</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>发热多久了？最高体温多少？</t>
+          <t>有没有胸痛、气短、头晕、多汗？</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>发热</t>
+          <t>咳嗽</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>有没有咳嗽、咽痛、腹泻、皮疹？</t>
+          <t>咳嗽多久了？</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>头晕</t>
+          <t>咳嗽</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>sputum</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>是旋转感（天旋地转）还是头重脚轻？</t>
+          <t>有没有痰？痰是什么颜色？</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>头晕</t>
+          <t>咳嗽</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>持续多久？是阵发还是持续？</t>
+          <t>有没有发热？体温多少？</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>肢体无力</t>
+          <t>发热</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>onset</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>无力是突然发生还是慢慢出现的？</t>
+          <t>发热多久了？最高体温多少？</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1372,21 +1816,241 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>肢体无力</t>
+          <t>发热</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>是单侧还是双侧？具体哪边？</t>
+          <t>有没有咳嗽、咽痛、腹泻、皮疹？</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>头痛</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>头痛在哪个部位（太阳穴、后脑勺、全头）？</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>头痛</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>是胀痛、跳痛还是刺痛？</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>头痛</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>accompanying</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>有没有恶心、呕吐、畏光、发热？</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>头晕</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>是旋转感（天旋地转）还是头重脚轻？</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>头晕</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>持续多久？是阵发还是持续？</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>肢体无力</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>onset</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>无力是突然发生还是慢慢出现的？</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>肢体无力</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>是单侧还是双侧？具体哪边？</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>尿频尿痛</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>尿频尿痛多久了？有没有血尿、发热？</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>皮疹</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>皮疹是什么样（红斑、丘疹、水疱）？分布在哪些部位？</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>皮疹</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>有没有接触过敏原、用药、进食特殊食物？</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>下腹痛</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>relation</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>腹痛与月经周期有关系吗？有没有阴道出血？</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1400,12 +2064,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
@@ -1574,32 +2238,320 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>内分泌科</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>内分泌代谢科</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>诊治糖尿病、甲状腺疾病、痛风、肥胖等代谢内分泌疾病</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>糖尿病|甲状腺|痛风</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>2型糖尿病|甲状腺功能亢进|甲状腺功能减退|痛风</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>URO</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>泌尿外科</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>泌尿科</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>诊治泌尿系统与男性生殖系统疾病，如尿频、尿急、尿痛、血尿、腰痛、结石等</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>结石|前列腺|感染</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>尿路感染|肾结石|前列腺增生|膀胱炎</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>GYN</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>妇科</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>妇科门诊</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>诊治女性生殖系统疾病，如月经不调、痛经、白带异常、下腹痛、盆腔炎等</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>月经病|炎症|肿瘤</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>阴道炎|月经不调|子宫肌瘤|盆腔炎</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>产科</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>围产科</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>诊治妊娠相关疾病与孕期保健，如早孕反应、先兆流产、妊娠期高血压等</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>孕期保健|高危妊娠</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>早孕反应|先兆流产|妊娠期高血压|孕期贫血</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>ORTH</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>骨科</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>骨外科</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>诊治骨骼、关节、脊柱与运动系统疾病，如腰背痛、关节痛、骨折、扭伤等</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>脊柱|关节|创伤</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>腰肌劳损|腰椎间盘突出|膝关节骨关节炎|骨折</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>DERM</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>皮肤科</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>皮肤病科</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>诊治皮肤、毛发、指甲疾病，如皮疹、瘙痒、湿疹、荨麻疹、痤疮等</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>过敏|感染|炎症</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>湿疹|荨麻疹|痤疮|带状疱疹</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>ENT</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>耳鼻喉科</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>五官科|耳鼻咽喉科</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>诊治耳、鼻、咽喉疾病，如咽痛、鼻塞、耳鸣、听力下降、扁桃体炎等</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>耳部|鼻部|咽喉</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>急性咽炎|过敏性鼻炎|急性中耳炎|扁桃体炎</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>OPH</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>眼病科</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>诊治眼部疾病，如眼红、眼痛、视力下降、视物模糊、干眼等</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>眼前节|眼底</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>结膜炎|干眼症|麦粒肿|青光眼</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>PSY</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>精神心理科</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>心理科|精神科</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>诊治失眠、焦虑、抑郁、惊恐等精神心理障碍</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>情绪障碍|睡眠障碍</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>失眠|焦虑症|抑郁症|惊恐障碍</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>EMER</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>急诊科</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>急诊|急救</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>处理急危重症，如剧烈胸痛、呼吸困难、大出血、昏迷、休克、严重外伤等</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>抢救|留观</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>急性心肌梗死|脑卒中|大出血|呼吸困难</t>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>急性心肌梗死|脑卒中|大出血|严重过敏</t>
         </is>
       </c>
     </row>
@@ -1614,11 +2566,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
@@ -1686,7 +2638,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>心内科医生</t>
+          <t>李心怡</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1713,7 +2665,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>呼吸科医生</t>
+          <t>陈呼吸</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1740,7 +2692,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>神经科医生</t>
+          <t>王神经</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1767,7 +2719,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>急诊科医生</t>
+          <t>赵内分</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1777,10 +2729,253 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>内分泌科</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>doctor06</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>钱泌尿</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>副主任医师</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>URO</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>泌尿外科</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>doctor07</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>孙妇科</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>主任医师</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>GYN</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>妇科</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>doctor08</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>周产科</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>主治医师</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>产科</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>doctor09</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>吴骨科</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>副主任医师</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>ORTH</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>骨科</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>doctor10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>郑皮肤</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>主治医师</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>DERM</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>皮肤科</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>doctor11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>冯耳鼻</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>副主任医师</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>ENT</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>耳鼻喉科</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>doctor12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>陈眼科</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>主治医师</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>OPH</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>doctor13</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>褚心理</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>副主任医师</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>PSY</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>精神心理科</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>doctor14</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>卫急诊</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>主治医师</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
           <t>EMER</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>急诊科</t>
         </is>
@@ -1797,13 +2992,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1933,7 +3128,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>急性胆囊炎|消化性溃疡穿孔|心肌梗死</t>
+          <t>急性胆囊炎|溃疡穿孔|心肌梗死</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1992,7 +3187,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>冠心病史|高血压|吸烟|糖尿病|年龄大</t>
+          <t>冠心病史|高血压|吸烟|糖尿病|高龄</t>
         </is>
       </c>
     </row>
@@ -2019,7 +3214,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>高盐饮食|肥胖|家族史|长期精神紧张</t>
+          <t>高盐饮食|肥胖|家族史|精神紧张</t>
         </is>
       </c>
     </row>
@@ -2122,7 +3317,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>慢阻肺|心源性哮喘|上气道异物</t>
+          <t>慢阻肺|心源性哮喘|气道异物</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -2154,7 +3349,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>长期吸烟|职业粉尘|年龄大</t>
+          <t>长期吸烟|职业粉尘|高龄</t>
         </is>
       </c>
     </row>
@@ -2269,54 +3464,1080 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>EMER</t>
+          <t>END</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>大出血</t>
+          <t>2型糖尿病</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>大量呕血|咯血|便血|外伤出血</t>
+          <t>多饮|多尿|多食|体重下降|乏力</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>出血性休克需立即处置</t>
+          <t>1型糖尿病|甲亢|尿崩症</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>肝硬化|消化性溃疡|抗凝药物</t>
+          <t>肥胖|家族史|高糖饮食|缺乏运动</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>甲状腺功能亢进</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>心悸|多汗|消瘦|手抖|易激动</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>甲减|焦虑症|心律失常</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>女性|自身免疫|碘摄入异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>甲状腺功能减退</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>乏力|怕冷|体重增加|便秘|水肿</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>贫血|抑郁症|肾病</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>女性|自身免疫|甲状腺手术史</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>痛风</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>关节红肿热痛|第一跖趾关节痛|夜间发作</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>类风湿关节炎|蜂窝织炎|假性痛风</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>高尿酸|饮酒|高嘌呤饮食|肥胖</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>URO</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>尿路感染</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>尿频|尿急|尿痛|下腹不适</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>膀胱炎|肾盂肾炎|性传播感染</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>女性|饮水少|憋尿|免疫力低</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>URO</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>肾结石</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>腰痛|血尿|肾绞痛|恶心呕吐</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>肾盂肾炎|胆囊炎|腰肌劳损</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>饮水少|高盐饮食|家族史|高温环境</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>URO</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>前列腺增生</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>尿频|夜尿增多|排尿困难|尿线细</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>前列腺癌|膀胱颈梗阻|尿路感染</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>老年男性|雄激素|家族史</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>URO</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>膀胱炎</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>尿频|尿急|尿痛|血尿</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>尿路感染|间质性膀胱炎|膀胱癌</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>女性|性生活|导尿|免疫力低</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>GYN</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>阴道炎</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>白带异常|外阴瘙痒|异味|灼痛</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>宫颈炎|盆腔炎|性传播感染</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>卫生习惯|免疫力低|抗生素滥用</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>GYN</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>月经不调</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>月经周期紊乱|经期延长|经量异常|痛经</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>多囊卵巢|子宫肌瘤|内分泌失调</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>精神压力|作息紊乱|肥胖|甲状腺疾病</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>GYN</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>子宫肌瘤</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>月经量多|经期延长|下腹包块|腹痛</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>子宫腺肌症|卵巢囊肿|子宫内膜癌</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>育龄女性|家族史|肥胖|雌激素</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>GYN</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>盆腔炎</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>下腹痛|白带增多|发热|性交痛</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>异位妊娠|阑尾炎|卵巢囊肿扭转</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>性传播感染|宫腔操作史|多性伴</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>早孕反应</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>停经|恶心|呕吐|乏力|乳房胀痛</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>胃肠炎|甲亢|葡萄胎</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>妊娠早期|多胎妊娠|心理因素</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>先兆流产</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>停经后阴道出血|下腹痛|腰酸</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>异位妊娠|葡萄胎|月经失调</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>高龄孕妇|既往流产史|劳累</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>妊娠期高血压</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>孕期血压升高|水肿|头痛|视物模糊</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>慢性高血压|子痫前期|肾病</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>初产妇|高龄|肥胖|多胎</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>孕期贫血</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>孕期乏力|头晕|面色苍白|心悸</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>缺铁性贫血|地中海贫血|营养不良</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>孕期铁需求增加|多胎|孕吐严重</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>ORTH</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>腰肌劳损</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>腰背酸痛|久坐加重|活动后减轻</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>腰椎间盘突出|强直性脊柱炎|肾结石</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>久坐|姿势不良|重体力劳动</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>ORTH</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>腰椎间盘突出</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>腰痛|下肢放射痛|麻木|活动受限</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>腰肌劳损|椎管狭窄|坐骨神经痛</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>久坐|重体力|肥胖|外伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>ORTH</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>膝关节骨关节炎</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>膝关节痛|活动受限|晨僵|摩擦感</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>类风湿关节炎|痛风|半月板损伤</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>高龄|肥胖|过度运动|既往损伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>ORTH</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>骨折</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>局部疼痛|肿胀|畸形|活动障碍</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>扭伤|脱位|骨肿瘤</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>外伤|骨质疏松|运动损伤|高龄</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>DERM</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>湿疹</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>皮疹|瘙痒|红斑|渗液|干燥脱屑</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>接触性皮炎|银屑病|真菌感染</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>过敏体质|干燥环境|精神压力</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>DERM</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>荨麻疹</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>风团|瘙痒|时起时消|皮肤划痕</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>湿疹|丘疹性荨麻疹|血管性水肿</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>食物或药物过敏|感染|寒冷刺激</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>DERM</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>痤疮</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>面部粉刺|丘疹|脓疱|结节</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>玫瑰痤疮|毛囊炎|脂溢性皮炎</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>青春期|油性皮肤|熬夜|高糖饮食</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>DERM</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>带状疱疹</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>单侧带状皮疹|灼痛|水疱|神经痛</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>单纯疱疹|接触性皮炎|神经痛</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>水痘史|免疫力低下|高龄|劳累</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>ENT</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>急性咽炎</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>咽痛|咽干|吞咽痛|发热</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>扁桃体炎|喉炎|流感</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>受凉|用嗓过度|烟酒刺激</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>ENT</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>过敏性鼻炎</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>鼻痒|喷嚏|清水鼻涕|鼻塞</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>感冒|血管运动性鼻炎|鼻息肉</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>过敏体质|花粉尘螨|季节变化</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>ENT</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>急性中耳炎</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>耳痛|听力下降|耳鸣|发热</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>外耳道炎|中耳积液|咽鼓管障碍</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>感冒后|儿童|游泳进水</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>ENT</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>扁桃体炎</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>咽痛|扁桃体肿大|发热|吞咽困难</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>咽炎|化脓性咽峡炎|传染性单核细胞增多</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>儿童青少年|受凉|免疫力低</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>OPH</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>结膜炎</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>眼红|眼痒|分泌物增多|异物感</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>角膜炎|干眼症|虹膜炎</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>细菌或病毒感染|过敏|用眼卫生差</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>OPH</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>干眼症</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>眼干|异物感|眼疲劳|视物模糊</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>结膜炎|角膜炎|视疲劳</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>长时间用眼|屏幕|干燥环境|高龄</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>OPH</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>麦粒肿</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>眼睑红肿|局部硬结|压痛|流泪</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>霰粒肿|眼睑脓肿|睑腺炎</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>用眼卫生差|睑板腺堵塞|糖尿病</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>OPH</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>青光眼</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>眼胀痛|视力下降|虹视|头痛</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>急性结膜炎|偏头痛|白内障</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>高龄|家族史|高度近视|糖尿病</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>PSY</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>失眠</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>入睡困难|易醒|早醒|日间疲倦</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>焦虑症|抑郁症|睡眠呼吸暂停</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>精神压力|作息紊乱|咖啡因|电子产品</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>PSY</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>焦虑症</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>紧张不安|心慌|多汗|坐立不安</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>甲亢|心脏神经症|抑郁</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>性格因素|精神压力|家族史</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>PSY</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>抑郁症</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>情绪低落|兴趣减退|乏力|睡眠障碍</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>甲减|焦虑症|双相障碍</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>家族史|重大事件|慢性疾病|性格</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>PSY</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>惊恐障碍</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>突发心慌|濒死感|呼吸困难|恐惧</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>心脏病|甲亢|低血糖</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>焦虑史|精神压力|家族史</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
           <t>EMER</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>呼吸困难</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>喘不上气|窒息感|发绀|端坐呼吸</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>气胸|肺栓塞|心衰|哮喘急性发作</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>心肺疾病|过敏|气道异物</t>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>急性心肌梗死</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>剧烈胸痛|大汗|濒死感|恶心</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>主动脉夹层|肺栓塞|急性心包炎</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>冠心病史|高血压|吸烟|糖尿病</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>EMER</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>脑卒中</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>突发言语不清|单侧肢体无力|口角歪斜|意识障碍</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>低血糖|癫痫|偏头痛</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>高血压|房颤|糖尿病|高龄</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>EMER</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>大出血</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>大量呕血|咯血|便血|外伤出血</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>出血性休克需立即处置</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>肝硬化|消化性溃疡|抗凝药物</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>EMER</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>严重过敏</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>皮疹|呼吸困难|喉头水肿|血压下降</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>过敏性休克|哮喘发作|血管性水肿</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>过敏史|药物食物接触|昆虫叮咬</t>
         </is>
       </c>
     </row>
@@ -2331,12 +4552,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -2387,7 +4608,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>急性胃肠炎以对症支持治疗为主，重点是补液与纠正电解质紊乱；抗生素仅用于明确的细菌感染或免疫低下人群。</t>
+          <t>以对症支持治疗为主，重点是补液与纠正电解质紊乱；抗生素仅用于明确的细菌感染或免疫低下人群。</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -2507,7 +4728,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>社区获得性肺炎依据CURB-65评分评估病情严重程度，轻症可门诊治疗，重症需住院。</t>
+          <t>依据CURB-65评分评估病情严重程度，轻症可门诊治疗，重症需住院，注意病原学检查。</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -2567,7 +4788,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>急性缺血性卒中发病4.5小时内可行静脉溶栓，时间就是大脑，需尽快评估转运。</t>
+          <t>发病4.5小时内可行静脉溶栓，时间就是大脑，需尽快评估转运至有条件的卒中中心。</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -2597,7 +4818,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>偏头痛急性期用止痛药或曲普坦类，频繁发作需预防性用药并避免诱因。</t>
+          <t>急性期用止痛药或曲普坦类，频繁发作需预防性用药并避免诱因，记录头痛日记。</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -2617,17 +4838,17 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>EMER</t>
+          <t>END</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>危重症早期识别原则</t>
+          <t>2型糖尿病防治指南要点</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>对剧烈胸痛、呼吸困难、大出血、昏迷、抽搐等症状，先评估生命体征并就地急救，同时呼叫120。</t>
+          <t>强调个体化血糖控制目标，生活方式干预贯穿全程，定期筛查并发症。</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -2639,6 +4860,576 @@
         <v>2023</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>痛风诊疗指南要点</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>急性期抗炎止痛，缓解期降尿酸治疗并长期达标，限制高嘌呤饮食与酒精。</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>URO</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>尿路感染诊治要点</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>依据感染部位与复杂程度选择抗生素，注意尿培养，避免滥用导致耐药。</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>URO</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>泌尿系结石诊疗要点</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>依据结石大小部位选择排石、体外碎石或手术，强调多饮水预防复发。</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>GYN</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>阴道炎诊治要点</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>依据病原学（细菌/真菌/滴虫）分類治疗，强调规范足疗程与伴侣同治。</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>GYN</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>子宫肌瘤诊治要点</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>依据症状、大小与生育需求选择随访、药物或手术治疗。</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>妊娠期高血压疾病诊治要点</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>重视孕期血压监测与尿蛋白筛查，子痫前期需及时评估终止妊娠时机。</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>孕期贫血防治要点</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>孕期常规筛查血红蛋白，缺铁性贫血补充铁剂并评估疗效。</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>ORTH</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>腰椎间盘突出诊治要点</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>多数患者保守治疗有效，出现马尾神经综合征需急诊手术。</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>ORTH</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>骨关节炎诊治要点</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>以运动与体重管理为基础，阶梯用药，晚期考虑关节置换。</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>DERM</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>湿疹诊疗要点</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>保湿是基础，外用药分级使用，避免诱因与过度清洁。</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>DERM</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>荨麻疹诊治要点</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>首选二代抗组胺药，慢性者需排查诱因并阶梯加量。</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>ENT</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>过敏性鼻炎诊治要点</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>避免过敏原，鼻用糖皮质激素与抗组胺药为一线治疗。</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>ENT</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>急性中耳炎诊治要点</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>儿童需评估听力，依据病情决定观察或抗生素治疗。</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>OPH</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>干眼症诊治要点</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>人工泪液为基础，强调用眼卫生与屏幕使用管理。</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>OPH</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>青光眼诊治要点</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>控制眼压为核心，定期视野检查，急性发作需紧急降眼压。</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>PSY</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>抑郁症诊治要点</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>轻中度可心理治疗，中重度需药物联合心理治疗，注意自杀风险评估。</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>PSY</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>失眠障碍诊治要点</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>首选认知行为治疗，药物短期使用并注意依赖性。</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>EMER</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>危重症早期识别原则</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>对剧烈胸痛、呼吸困难、大出血、昏迷、抽搐等，先评估生命体征并就地急救，同时呼叫120。</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>示例指南片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>EMER</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>心肺复苏与急救要点</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>心搏骤停立即胸外按压，尽早电除颤，把握黄金4分钟。</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>示例指南片段</t>
         </is>
@@ -2655,7 +5446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3124,6 +5915,1032 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2型糖尿病</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>E11.9</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>第四章 内分泌营养代谢疾病</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>非胰岛素依赖型糖尿病</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>1型糖尿病（E10）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>甲状腺功能亢进</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>E05.9</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>第四章 内分泌营养代谢疾病</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>毒性甲状腺肿</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>甲状腺炎（E06）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>甲状腺功能减退</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>E03.9</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>第四章 内分泌营养代谢疾病</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>原发性甲减</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>垂体性甲减（E23.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>痛风</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>M10.9</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>第十三章 肌肉骨骼系统疾病</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>原发性痛风</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>假性痛风（M11.2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>尿路感染</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>N39.0</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>第十四章 泌尿生殖系统疾病</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>泌尿系统感染</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>肾盂肾炎（N10）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>肾结石</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N20.0</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>第十四章 泌尿生殖系统疾病</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>肾结石、输尿管结石</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>胆结石（K80）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>前列腺增生</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>N40</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>第十四章 泌尿生殖系统疾病</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>良性前列腺增生</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>前列腺癌（C61）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>膀胱炎</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>N30.9</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>第十四章 泌尿生殖系统疾病</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>膀胱炎</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>间质性膀胱炎（N30.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>阴道炎</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N76.0</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>第十四章 泌尿生殖系统疾病</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>急性阴道炎</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>宫颈炎（N72）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>月经不调</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>N92.6</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>第十四章 泌尿生殖系统疾病</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>不规则月经</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>闭经（N91）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>子宫肌瘤</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>D25.9</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>第十四章 泌尿生殖系统疾病</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>子宫平滑肌瘤</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>子宫恶性肿瘤（C54）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>盆腔炎</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N73.9</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>第十四章 泌尿生殖系统疾病</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>女性盆腔炎性疾病</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>异位妊娠（O00）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>早孕反应</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>O21.9</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>第十五章 妊娠分娩产褥期</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>妊娠剧吐</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>妊娠期肝病（O26.6）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>先兆流产</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>O20.0</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>第十五章 妊娠分娩产褥期</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>先兆流产</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>异位妊娠（O00）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>妊娠期高血压</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>O13</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>第十五章 妊娠分娩产褥期</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>妊娠期高血压</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>慢性高血压（I10）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>孕期贫血</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>O99.0</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>第十五章 妊娠分娩产褥期</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>妊娠合并贫血</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>产后贫血（O90.8）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>腰肌劳损</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>M54.5</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>第十三章 肌肉骨骼系统疾病</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>腰痛</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>腰椎间盘突出（M51.2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>腰椎间盘突出</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>M51.2</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>第十三章 肌肉骨骼系统疾病</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>腰椎间盘突出伴神经根病</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>椎管狭窄（M48.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>膝关节骨关节炎</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>M17.9</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>第十三章 肌肉骨骼系统疾病</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>膝关节骨关节炎</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>类风湿关节炎（M06）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>骨折</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>T14.2</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>第十九章 损伤中毒</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>未特指部位骨折</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>脱位（T14.3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>湿疹</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>L30.9</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>第十二章 皮肤和皮下组织疾病</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>湿疹</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>接触性皮炎（L25）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>荨麻疹</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>L50.9</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>第十二章 皮肤和皮下组织疾病</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>荨麻疹</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>血管性水肿（T78.3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>痤疮</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>L70.9</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>第十二章 皮肤和皮下组织疾病</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>痤疮</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>玫瑰痤疮（L71）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>带状疱疹</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>B02.9</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>第一章 某些传染病和寄生虫病</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>带状疱疹</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>单纯疱疹（B00）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>急性咽炎</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>J02.9</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>第十章 呼吸系统疾病</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>急性咽炎</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>扁桃体炎（J03）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>过敏性鼻炎</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>J30.9</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>第十章 呼吸系统疾病</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>变应性鼻炎</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>非过敏性鼻炎（J31.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>急性中耳炎</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>H66.9</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>第八章 耳和乳突疾病</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>中耳炎</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>外耳道炎（H60）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>扁桃体炎</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>J03.9</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>第十章 呼吸系统疾病</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>急性扁桃体炎</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>咽炎（J02）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>结膜炎</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>H10.9</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>第七章 眼和附器疾病</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>结膜炎</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>角膜炎（H16）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>干眼症</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>H11.9</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>第七章 眼和附器疾病</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>干眼综合征</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>结膜炎（H10）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>麦粒肿</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>H00.0</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>第七章 眼和附器疾病</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>睑腺炎</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>霰粒肿（H00.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>青光眼</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>H40.9</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>第七章 眼和附器疾病</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>青光眼</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>白内障（H25）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>失眠</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>G47.0</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>第六章 神经系统疾病</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>失眠障碍</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>睡眠呼吸暂停（G47.3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>焦虑症</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>F41.9</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>第五章 精神和行为障碍</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>焦虑障碍</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>抑郁症（F32）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>抑郁症</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>F32.9</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>第五章 精神和行为障碍</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>抑郁发作</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>双相障碍（F31）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>惊恐障碍</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>F41.0</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>第五章 精神和行为障碍</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>惊恐障碍</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>广泛性焦虑（F41.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>大出血</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>R58</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>第十八章 症状、体征</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>出血</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>咯血（R04）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>严重过敏</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>T78.2</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>第十九章 损伤中毒</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>过敏性休克</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>血管性水肿（T78.3）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3135,12 +6952,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -3279,61 +7096,61 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>胸痛</t>
+          <t>便秘</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>胸口疼|心口疼|胸闷痛</t>
+          <t>大便干结|排便困难</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>胸部</t>
+          <t>腹部</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>急性/慢性</t>
+          <t>慢性</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>胸闷</t>
+          <t>便血</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>胸口发闷|气不够用</t>
+          <t>大便带血|黑便</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>胸部</t>
+          <t>腹部</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>阵发性</t>
+          <t>急性/慢性</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>心悸</t>
+          <t>腹胀</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>心慌|心跳快|心里扑腾</t>
+          <t>肚子胀|胃胀</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>胸部</t>
+          <t>腹部</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -3345,12 +7162,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>呼吸困难</t>
+          <t>胸痛</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>喘不上气|气短|憋气</t>
+          <t>胸口疼|心口疼|胸闷痛</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -3367,12 +7184,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>咳嗽</t>
+          <t>胸闷</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>干咳|咳嗦</t>
+          <t>胸口发闷|气不够用</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -3382,19 +7199,19 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>急性/慢性</t>
+          <t>阵发性</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>咳痰</t>
+          <t>心悸</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>吐痰|有痰</t>
+          <t>心慌|心跳快|心里扑腾</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -3404,24 +7221,24 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>急性/慢性</t>
+          <t>阵发性</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>发热</t>
+          <t>心前区痛</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>发烧|体温高|低烧</t>
+          <t>心口痛|前胸痛</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>全身</t>
+          <t>胸部</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -3433,17 +7250,17 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>头痛</t>
+          <t>呼吸困难</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>头疼|脑袋疼|太阳穴疼</t>
+          <t>喘不上气|气短|憋气</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>头部</t>
+          <t>胸部</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3455,17 +7272,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>头晕</t>
+          <t>咳嗽</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>头昏|眩晕|天旋地转</t>
+          <t>干咳|咳嗦</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>头部</t>
+          <t>胸部</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -3477,17 +7294,17 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>肢体无力</t>
+          <t>咳痰</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>没劲|手脚没力气|偏瘫</t>
+          <t>吐痰|有痰</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>四肢</t>
+          <t>胸部</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3499,61 +7316,61 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>麻木</t>
+          <t>咯血</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>发麻|手麻脚麻</t>
+          <t>咳血|吐血</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>四肢</t>
+          <t>胸部</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>阵发性</t>
+          <t>急性</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>抽搐</t>
+          <t>喘息</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>抽筋|惊厥|抽风</t>
+          <t>喘鸣|气道响</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>全身</t>
+          <t>胸部</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>急性</t>
+          <t>阵发性</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>意识障碍</t>
+          <t>发热</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>昏迷|晕倒|不省人事|晕厥</t>
+          <t>发烧|体温高|低烧</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>头部</t>
+          <t>全身</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3565,44 +7382,990 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>便血</t>
+          <t>乏力</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>大便带血|黑便</t>
+          <t>没力气|疲倦|疲乏</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>腹部</t>
+          <t>全身</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>急性</t>
+          <t>急性/慢性</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>咯血</t>
+          <t>盗汗</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>咳血|吐血</t>
+          <t>夜间出汗|睡着出汗</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>胸部</t>
+          <t>全身</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
+          <t>慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>体重下降</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>消瘦|掉秤</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>全身</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>水肿</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>浮肿|腿肿</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>全身/下肢</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>头痛</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>头疼|脑袋疼|太阳穴疼</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>头部</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>急性/慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>头晕</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>头昏|眩晕|天旋地转</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>头部</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>急性/慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>眩晕</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>旋转感|天旋地转</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>头部</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>阵发性</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>肢体无力</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>没劲|手脚没力气|偏瘫</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>四肢</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>急性/慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>麻木</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>发麻|手麻脚麻</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>四肢</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>阵发性</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>抽搐</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>抽筋|惊厥|抽风</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>全身</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
           <t>急性</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>意识障碍</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>昏迷|晕倒|不省人事|晕厥</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>头部</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>急性</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>面瘫</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>口眼歪斜|嘴歪</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>面部</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>急性</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>言语不清</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>说话含糊|吐字不清</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>口咽</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>急性</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>多饮</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>喝水多|口渴</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>全身</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>多尿</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>尿多|尿量增多</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>泌尿</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>尿频</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>小便次数多|老想尿</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>泌尿</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>急性/慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>尿急</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>憋不住尿</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>泌尿</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>急性</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>尿痛</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>排尿疼|小便疼</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>泌尿</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>急性</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>血尿</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>尿血|小便带血</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>泌尿</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>急性/慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>排尿困难</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>尿不出来|尿线细</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>泌尿</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>腰痛</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>腰疼|腰部酸痛</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>腰部</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>急性/慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>关节痛</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>关节疼|关节肿胀</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>关节</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>急性/慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>关节红肿</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>关节发红|关节肿痛</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>关节</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>急性</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>腰背痛</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>后背痛|腰酸背痛</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>腰背</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>颈痛</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>脖子疼|颈椎痛</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>颈部</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>下腹痛</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>小肚子疼|下腹部疼痛</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>下腹部</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>急性/慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>白带异常</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>白带多|白带异味</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>生殖</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>阴道出血</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>下身出血|不规则出血</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>生殖</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>急性/慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>月经不调</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>月经紊乱|例假不准</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>生殖</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>痛经</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>月经痛|经期腹痛</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>下腹部</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>周期性</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>停经</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>月经停了|闭经</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>生殖</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>皮疹</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>起疹子|皮肤红点</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>皮肤</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>急性/慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>瘙痒</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>发痒|痒</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>皮肤</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>急性/慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>风团</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>风疹块|皮肤凸起</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>皮肤</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>阵发性</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>水疱</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>起泡|疱疹</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>皮肤</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>急性</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>咽痛</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>嗓子疼|喉咙痛</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>咽喉</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>急性</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>鼻塞</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>鼻子不通|鼻堵</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>鼻部</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>急性/慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>流涕</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>流鼻涕|鼻涕多</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>鼻部</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>急性</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>耳鸣</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>耳朵响|嗡嗡响</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>耳部</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>急性/慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>耳痛</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>耳朵疼</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>耳部</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>急性</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>眼红</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>眼睛发红|眼充血</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>眼部</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>急性</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>视力下降</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>看不清|视物模糊</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>眼部</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>急性/慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>失眠</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>睡不着|入睡困难|睡眠差</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>全身</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>情绪低落</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>心情差|高兴不起来</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>心理</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>慢性</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>焦虑</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>紧张|坐立不安|心慌</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>心理</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>慢性</t>
         </is>
       </c>
     </row>
@@ -3617,7 +8380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3960,6 +8723,156 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>RF11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>宫外孕破裂</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>停经后剧烈腹痛|阴道出血伴腹痛|头晕晕厥</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>GUIDE_TO_EMERGENCY</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>育龄女性停经后剧烈腹痛，请立即就医</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>RF12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>急性中毒</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>误服药物|农药中毒|一氧化碳中毒|吞服异物</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>GUIDE_TO_EMERGENCY</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>疑似中毒，请立即拨打120并携带毒物样本</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>RF13</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>重度脱水</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>婴幼儿腹泻伴精神萎靡|尿量极少|囟门凹陷</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>GUIDE_TO_EMERGENCY</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>孩子可能重度脱水，请立即就医</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>RF14</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>颅脑外伤</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>头部外伤后呕吐|意识改变|耳鼻流血</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>GUIDE_TO_EMERGENCY</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>头部外伤后异常，请立即就医</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>RF15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>血糖危象</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>糖尿病伴意识模糊|极度口渴多尿|呼吸深快</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>GUIDE_TO_EMERGENCY</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>可能发生血糖危象，请立即就医</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3971,7 +8884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4270,6 +9183,230 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>ACEI类（卡托普利）</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>妊娠</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>禁用</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>孕妇</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>妊娠中晚期可致胎儿损害</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>他汀类</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>妊娠/肝病</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>慎用</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>孕妇及肝病患者</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>监测肝功能</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>甲硝唑</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>妊娠早期</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>禁用</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>孕早期</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>孕早期禁用</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>华法林</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>妊娠</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>禁用</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>孕妇</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>致畸风险</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>布洛芬</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>消化性溃疡</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>慎用</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>胃溃疡患者</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>加重消化道出血风险</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>甲巯咪唑</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>妊娠早期</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>慎用</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>孕早期</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>孕早期首选丙硫氧嘧啶</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>异维A酸</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>妊娠</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>禁用</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>育龄女性</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>强致畸，需严格避孕</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kb/医学知识库源数据.xlsx
+++ b/kb/医学知识库源数据.xlsx
@@ -1217,7 +1217,11 @@
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
       <c r="F24" s="3" t="n">
         <v>10</v>
       </c>
@@ -6185,7 +6189,11 @@
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr"/>
-      <c r="E208" s="3" t="inlineStr"/>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
       <c r="F208" s="3" t="n">
         <v>8</v>
       </c>
@@ -6239,7 +6247,11 @@
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr"/>
-      <c r="E210" s="3" t="inlineStr"/>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
       <c r="F210" s="3" t="n">
         <v>8</v>
       </c>
@@ -6266,7 +6278,11 @@
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr"/>
-      <c r="E211" s="3" t="inlineStr"/>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
       <c r="F211" s="3" t="n">
         <v>8</v>
       </c>
@@ -6293,7 +6309,11 @@
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr"/>
-      <c r="E212" s="3" t="inlineStr"/>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
       <c r="F212" s="3" t="n">
         <v>8</v>
       </c>
@@ -6320,7 +6340,11 @@
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr"/>
-      <c r="E213" s="3" t="inlineStr"/>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
       <c r="F213" s="3" t="n">
         <v>8</v>
       </c>
@@ -6347,7 +6371,11 @@
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr"/>
-      <c r="E214" s="3" t="inlineStr"/>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
       <c r="F214" s="3" t="n">
         <v>8</v>
       </c>
@@ -6374,7 +6402,11 @@
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr"/>
-      <c r="E215" s="3" t="inlineStr"/>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
       <c r="F215" s="3" t="n">
         <v>8</v>
       </c>
@@ -6401,7 +6433,11 @@
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr"/>
-      <c r="E216" s="3" t="inlineStr"/>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
       <c r="F216" s="3" t="n">
         <v>8</v>
       </c>
@@ -6428,7 +6464,11 @@
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr"/>
-      <c r="E217" s="3" t="inlineStr"/>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
       <c r="F217" s="3" t="n">
         <v>8</v>
       </c>
@@ -6671,7 +6711,11 @@
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr"/>
-      <c r="E226" s="3" t="inlineStr"/>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
       <c r="F226" s="3" t="n">
         <v>8</v>
       </c>
@@ -6743,12 +6787,12 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>GYN</t>
+          <t>URO</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>妇科</t>
+          <t>泌尿外科</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr"/>
@@ -6770,12 +6814,12 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>GYN</t>
+          <t>URO</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>妇科</t>
+          <t>泌尿外科</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr"/>
@@ -6797,12 +6841,12 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>GYN</t>
+          <t>URO</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>妇科</t>
+          <t>泌尿外科</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr"/>

--- a/kb/医学知识库源数据.xlsx
+++ b/kb/医学知识库源数据.xlsx
@@ -54951,7 +54951,7 @@
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
@@ -55002,7 +55002,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>剧烈胸痛|压榨性胸痛|胸痛伴出汗|胸痛伴放射</t>
+          <t>剧烈胸痛|压榨性胸痛|胸痛伴出汗|胸痛冒冷汗|胸痛出冷汗|胸痛伴冷汗|胸痛伴放射|心梗</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">

--- a/kb/医学知识库源数据.xlsx
+++ b/kb/医学知识库源数据.xlsx
@@ -7416,7 +7416,7 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>疼痛具体在哪个部位（上腹/下腹/左右侧）？</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>疼了多久了？是持续还是阵发？</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>疼痛是什么样的（绞痛/胀痛/隐痛/烧灼痛）？</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>有没有腹泻、恶心、呕吐、发热？</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>severity</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>疼痛程度如何（轻/中/重）？</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -7545,17 +7545,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>腹痛</t>
+          <t>腹泻</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>腹泻多久了？</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -7565,17 +7565,17 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>腹痛</t>
+          <t>腹泻</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>frequency</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>一天腹泻几次？大便是什么样子？</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -7585,17 +7585,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>腹痛</t>
+          <t>腹泻</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>有没有腹痛、发热、呕吐、脱水？</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -7605,17 +7605,17 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>腹痛</t>
+          <t>腹泻</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>有没有吃不干净的东西？</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -7625,17 +7625,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>腹痛</t>
+          <t>腹泻</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>severity</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有精神差、尿少？</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -7645,17 +7645,17 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>腹泻</t>
+          <t>恶心</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>恶心多久了？</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -7665,17 +7665,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>腹泻</t>
+          <t>恶心</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>和进食有关吗？</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -7685,17 +7685,17 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>腹泻</t>
+          <t>恶心</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>有没有呕吐、腹痛、头痛？</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -7705,7 +7705,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>腹泻</t>
+          <t>恶心</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>是否影响进食？</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -7725,17 +7725,17 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>腹泻</t>
+          <t>恶心</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>以前有没有类似情况？</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -7745,17 +7745,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>腹泻</t>
+          <t>呕吐</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>呕吐多久了？</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -7765,17 +7765,17 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>腹泻</t>
+          <t>呕吐</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>frequency</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>吐了几次？吐的是什么？</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -7785,17 +7785,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>腹泻</t>
+          <t>呕吐</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>进食后还是空腹？</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -7805,17 +7805,17 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>腹泻</t>
+          <t>呕吐</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>有没有腹痛、发热、头痛？</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -7825,17 +7825,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>腹泻</t>
+          <t>呕吐</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>severity</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有脱水表现？</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -7845,17 +7845,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>恶心</t>
+          <t>胸痛</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>胸痛是什么样的（压榨/针刺/烧灼）？</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -7865,17 +7865,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>恶心</t>
+          <t>胸痛</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>radiation</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>有没有放射到左臂、下颌或后背？</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -7885,17 +7885,17 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>恶心</t>
+          <t>胸痛</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>什么情况下加重（活动/劳累/深呼吸）？</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -7905,17 +7905,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>恶心</t>
+          <t>胸痛</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>有没有出汗、气短、恶心？</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -7925,17 +7925,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>恶心</t>
+          <t>胸痛</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>每次持续多久？</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -7945,17 +7945,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>恶心</t>
+          <t>胸闷</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>胸闷什么情况下出现（活动/休息/夜间）？</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -7965,17 +7965,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>恶心</t>
+          <t>胸闷</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>每次持续多久？能否自行缓解？</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -7985,17 +7985,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>恶心</t>
+          <t>胸闷</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>有没有胸痛、气短、心悸？</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -8005,17 +8005,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>恶心</t>
+          <t>胸闷</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>radiation</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>有没有放射感？</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
@@ -8025,17 +8025,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>恶心</t>
+          <t>胸闷</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有心脏病史？</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
@@ -8045,17 +8045,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>呕吐</t>
+          <t>心悸</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>心慌什么情况下出现？</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
@@ -8065,7 +8065,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>呕吐</t>
+          <t>心悸</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>每次持续多久？</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -8085,7 +8085,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>呕吐</t>
+          <t>心悸</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>是心跳快、乱还是重？</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
@@ -8105,17 +8105,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>呕吐</t>
+          <t>心悸</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>有没有胸痛、气短、头晕、多汗？</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
@@ -8125,17 +8125,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>呕吐</t>
+          <t>心悸</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有甲亢或心脏病史？</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
@@ -8145,17 +8145,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>呕吐</t>
+          <t>咳嗽</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>咳嗽多久了？</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -8165,17 +8165,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>呕吐</t>
+          <t>咳嗽</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>sputum</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>有没有痰？痰是什么颜色？</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
@@ -8185,17 +8185,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>呕吐</t>
+          <t>咳嗽</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>有没有发热？体温多少？</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
@@ -8205,17 +8205,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>呕吐</t>
+          <t>咳嗽</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>夜间或活动后加重吗？</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
@@ -8225,17 +8225,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>呕吐</t>
+          <t>咳嗽</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有气短、胸痛？</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
@@ -8245,17 +8245,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>胸痛</t>
+          <t>咳痰</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>痰是什么颜色（白/黄/绿/带血）？</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
@@ -8265,17 +8265,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>胸痛</t>
+          <t>咳痰</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>痰量多不多？</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
@@ -8285,17 +8285,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>胸痛</t>
+          <t>咳痰</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>咳痰多久了？</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
@@ -8305,17 +8305,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>胸痛</t>
+          <t>咳痰</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>有没有发热？</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
@@ -8325,17 +8325,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>胸痛</t>
+          <t>咳痰</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有气短、胸痛？</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
@@ -8345,17 +8345,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>胸痛</t>
+          <t>发热</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>发热多久了？</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
@@ -8365,17 +8365,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>胸痛</t>
+          <t>发热</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>degree</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>最高体温多少？</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
@@ -8385,17 +8385,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>胸痛</t>
+          <t>发热</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>是持续还是忽高忽低？</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
@@ -8405,17 +8405,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>胸痛</t>
+          <t>发热</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>有没有咳嗽、咽痛、腹泻、皮疹？</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
@@ -8425,17 +8425,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>胸痛</t>
+          <t>发热</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有接触发热病人或旅行史？</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
@@ -8445,7 +8445,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>胸闷</t>
+          <t>头痛</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>头痛在哪个部位（太阳穴/后脑勺/全头）？</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
@@ -8465,17 +8465,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>胸闷</t>
+          <t>头痛</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>是胀痛、跳痛还是刺痛？</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
@@ -8485,17 +8485,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>胸闷</t>
+          <t>头痛</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>有没有恶心、呕吐、畏光、发热？</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
@@ -8505,17 +8505,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>胸闷</t>
+          <t>头痛</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>什么情况下加重？</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
@@ -8525,17 +8525,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>胸闷</t>
+          <t>头痛</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>severity</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>疼痛程度如何？</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
@@ -8545,17 +8545,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>胸闷</t>
+          <t>头晕</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>是旋转感（天旋地转）还是头重脚轻？</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
@@ -8565,17 +8565,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>胸闷</t>
+          <t>头晕</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>持续多久？是阵发还是持续？</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
@@ -8585,17 +8585,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>胸闷</t>
+          <t>头晕</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>体位变化时加重吗？</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
@@ -8605,17 +8605,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>胸闷</t>
+          <t>头晕</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>有没有恶心、耳鸣、肢体无力？</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
@@ -8625,17 +8625,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>胸闷</t>
+          <t>头晕</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有高血压、颈椎病？</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
@@ -8645,17 +8645,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>心悸</t>
+          <t>眩晕</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>眩晕持续多久？</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
@@ -8665,17 +8665,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>心悸</t>
+          <t>眩晕</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>头位变动时诱发吗？</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
@@ -8685,17 +8685,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>心悸</t>
+          <t>眩晕</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>有没有耳鸣、听力下降、恶心？</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
@@ -8705,17 +8705,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>心悸</t>
+          <t>眩晕</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>是天旋地转还是摇晃感？</t>
         </is>
       </c>
       <c r="D65" s="3" t="n">
@@ -8725,17 +8725,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>心悸</t>
+          <t>眩晕</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>以前有没有类似发作？</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
@@ -8745,17 +8745,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>心悸</t>
+          <t>肢体无力</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>onset</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>无力是突然发生还是慢慢出现的？</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
@@ -8765,17 +8765,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>心悸</t>
+          <t>肢体无力</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>是单侧还是双侧？具体哪边？</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
@@ -8785,17 +8785,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>心悸</t>
+          <t>肢体无力</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>有没有言语不清、口角歪斜？</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
@@ -8805,17 +8805,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>心悸</t>
+          <t>肢体无力</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>progression</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>是加重还是好转？</t>
         </is>
       </c>
       <c r="D70" s="3" t="n">
@@ -8825,17 +8825,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>心悸</t>
+          <t>肢体无力</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有高血压、糖尿病？</t>
         </is>
       </c>
       <c r="D71" s="3" t="n">
@@ -8845,7 +8845,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>咳嗽</t>
+          <t>麻木</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>麻木在哪个部位？</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
@@ -8865,17 +8865,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>咳嗽</t>
+          <t>麻木</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>是持续还是阵发？</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
@@ -8885,17 +8885,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>咳嗽</t>
+          <t>麻木</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>有没有无力、疼痛？</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
@@ -8905,17 +8905,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>咳嗽</t>
+          <t>麻木</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>什么姿势下出现？</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
@@ -8925,17 +8925,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>咳嗽</t>
+          <t>麻木</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有糖尿病、颈椎病？</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
@@ -8945,17 +8945,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>咳嗽</t>
+          <t>尿频</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>尿频多久了？</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
@@ -8965,17 +8965,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>咳嗽</t>
+          <t>尿频</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>frequency</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>一天几次？夜尿几次？</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
@@ -8985,17 +8985,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>咳嗽</t>
+          <t>尿频</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>有没有尿痛、血尿、发热？</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
@@ -9005,17 +9005,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>咳嗽</t>
+          <t>尿频</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>和饮水、情绪有关吗？</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
@@ -9025,17 +9025,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>咳嗽</t>
+          <t>尿频</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有前列腺或妇科病史？</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
@@ -9045,17 +9045,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>咳痰</t>
+          <t>尿急</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>尿急多久了？</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
@@ -9065,17 +9065,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>咳痰</t>
+          <t>尿急</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>有没有尿痛、尿频、血尿？</t>
         </is>
       </c>
       <c r="D83" s="3" t="n">
@@ -9085,17 +9085,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>咳痰</t>
+          <t>尿急</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>憋不住时有没有漏尿？</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
@@ -9105,7 +9105,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>咳痰</t>
+          <t>尿急</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>是否影响生活？</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
@@ -9125,17 +9125,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>咳痰</t>
+          <t>尿急</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有尿路感染史？</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
@@ -9145,17 +9145,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>咳痰</t>
+          <t>尿痛</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>尿痛多久了？</t>
         </is>
       </c>
       <c r="D87" s="3" t="n">
@@ -9165,17 +9165,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>咳痰</t>
+          <t>尿痛</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>是排尿开始痛还是全程痛？</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
@@ -9185,17 +9185,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>咳痰</t>
+          <t>尿痛</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>有没有尿频、尿急、血尿、发热？</t>
         </is>
       </c>
       <c r="D89" s="3" t="n">
@@ -9205,17 +9205,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>咳痰</t>
+          <t>尿痛</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>和性生活有关吗？</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
@@ -9225,17 +9225,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>咳痰</t>
+          <t>尿痛</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有尿路感染史？</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
@@ -9245,17 +9245,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>发热</t>
+          <t>血尿</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>是肉眼可见还是镜下血尿？</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
@@ -9265,7 +9265,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>发热</t>
+          <t>血尿</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -9285,17 +9285,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>发热</t>
+          <t>血尿</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>有没有腰痛、尿痛、发热？</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
@@ -9305,17 +9305,17 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>发热</t>
+          <t>血尿</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>和运动、月经有关吗？</t>
         </is>
       </c>
       <c r="D95" s="3" t="n">
@@ -9325,17 +9325,17 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>发热</t>
+          <t>血尿</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有结石、肿瘤病史？</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
@@ -9345,17 +9345,17 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>发热</t>
+          <t>腰痛</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>腰痛在哪个部位？</t>
         </is>
       </c>
       <c r="D97" s="3" t="n">
@@ -9365,17 +9365,17 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>发热</t>
+          <t>腰痛</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>是酸痛、绞痛还是刺痛？</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
@@ -9385,17 +9385,17 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>发热</t>
+          <t>腰痛</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>什么姿势或动作加重？</t>
         </is>
       </c>
       <c r="D99" s="3" t="n">
@@ -9405,17 +9405,17 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>发热</t>
+          <t>腰痛</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>有没有下肢放射痛、麻木？</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
@@ -9425,17 +9425,17 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>发热</t>
+          <t>腰痛</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有外伤或久坐？</t>
         </is>
       </c>
       <c r="D101" s="3" t="n">
@@ -9445,7 +9445,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>头痛</t>
+          <t>关节痛</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>哪个关节痛？单侧还是双侧？</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
@@ -9465,17 +9465,17 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>头痛</t>
+          <t>关节痛</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>是肿痛、刺痛还是酸痛？</t>
         </is>
       </c>
       <c r="D103" s="3" t="n">
@@ -9485,17 +9485,17 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>头痛</t>
+          <t>关节痛</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>痛了多久？晨僵吗？</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
@@ -9505,17 +9505,17 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>头痛</t>
+          <t>关节痛</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>活动后加重还是缓解？</t>
         </is>
       </c>
       <c r="D105" s="3" t="n">
@@ -9525,17 +9525,17 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>头痛</t>
+          <t>关节痛</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有红肿、发热？</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
@@ -9545,17 +9545,17 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>头痛</t>
+          <t>皮疹</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>皮疹在哪些部位？</t>
         </is>
       </c>
       <c r="D107" s="3" t="n">
@@ -9565,17 +9565,17 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>头痛</t>
+          <t>皮疹</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>是什么样（红斑/丘疹/水疱/风团）？</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
@@ -9585,17 +9585,17 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>头痛</t>
+          <t>皮疹</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>出现多久了？</t>
         </is>
       </c>
       <c r="D109" s="3" t="n">
@@ -9605,17 +9605,17 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>头痛</t>
+          <t>皮疹</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>有没有接触过敏原、用药、进食特殊食物？</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
@@ -9625,17 +9625,17 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>头痛</t>
+          <t>皮疹</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有瘙痒、发热？</t>
         </is>
       </c>
       <c r="D111" s="3" t="n">
@@ -9645,7 +9645,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>头晕</t>
+          <t>瘙痒</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>哪里痒？范围多大？</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
@@ -9665,7 +9665,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>头晕</t>
+          <t>瘙痒</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>痒了多久？</t>
         </is>
       </c>
       <c r="D113" s="3" t="n">
@@ -9685,7 +9685,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>头晕</t>
+          <t>瘙痒</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>是阵发还是持续？夜间加重吗？</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
@@ -9705,17 +9705,17 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>头晕</t>
+          <t>瘙痒</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>什么情况下加重？</t>
         </is>
       </c>
       <c r="D115" s="3" t="n">
@@ -9725,17 +9725,17 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>头晕</t>
+          <t>瘙痒</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有皮疹、干燥？</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
@@ -9745,17 +9745,17 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>头晕</t>
+          <t>咽痛</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>咽痛多久了？</t>
         </is>
       </c>
       <c r="D117" s="3" t="n">
@@ -9765,17 +9765,17 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>头晕</t>
+          <t>咽痛</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>severity</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>吞咽时疼吗？影响进食吗？</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
@@ -9785,17 +9785,17 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>头晕</t>
+          <t>咽痛</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>有没有发热、咳嗽、扁桃体肿大？</t>
         </is>
       </c>
       <c r="D119" s="3" t="n">
@@ -9805,17 +9805,17 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>头晕</t>
+          <t>咽痛</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>有没有受凉或用嗓过度？</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
@@ -9825,17 +9825,17 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>头晕</t>
+          <t>咽痛</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>以前有没有反复咽痛？</t>
         </is>
       </c>
       <c r="D121" s="3" t="n">
@@ -9845,17 +9845,17 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>眩晕</t>
+          <t>鼻塞</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>鼻塞多久了？</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
@@ -9865,17 +9865,17 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>眩晕</t>
+          <t>鼻塞</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>是单侧还是双侧？持续还是阵发？</t>
         </is>
       </c>
       <c r="D123" s="3" t="n">
@@ -9885,17 +9885,17 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>眩晕</t>
+          <t>鼻塞</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>有没有流涕、喷嚏、鼻痒？</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
@@ -9905,17 +9905,17 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>眩晕</t>
+          <t>鼻塞</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>季节性或接触过敏原时加重吗？</t>
         </is>
       </c>
       <c r="D125" s="3" t="n">
@@ -9925,17 +9925,17 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>眩晕</t>
+          <t>鼻塞</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有鼻炎史？</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -9945,17 +9945,17 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>眩晕</t>
+          <t>耳鸣</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>耳鸣是什么样的声音？</t>
         </is>
       </c>
       <c r="D127" s="3" t="n">
@@ -9965,17 +9965,17 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>眩晕</t>
+          <t>耳鸣</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>持续多久了？</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
@@ -9985,17 +9985,17 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>眩晕</t>
+          <t>耳鸣</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>单侧还是双侧？</t>
         </is>
       </c>
       <c r="D129" s="3" t="n">
@@ -10005,17 +10005,17 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>眩晕</t>
+          <t>耳鸣</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>有没有听力下降、眩晕？</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
@@ -10025,17 +10025,17 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>眩晕</t>
+          <t>耳鸣</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有噪声暴露或耳部疾病？</t>
         </is>
       </c>
       <c r="D131" s="3" t="n">
@@ -10045,17 +10045,17 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>肢体无力</t>
+          <t>眼红</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>眼红多久了？</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
@@ -10065,17 +10065,17 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>肢体无力</t>
+          <t>眼红</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>有没有眼痛、眼痒、分泌物？</t>
         </is>
       </c>
       <c r="D133" s="3" t="n">
@@ -10085,17 +10085,17 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>肢体无力</t>
+          <t>眼红</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>单眼还是双眼？</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
@@ -10105,17 +10105,17 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>肢体无力</t>
+          <t>眼红</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>有没有接触刺激物或揉眼？</t>
         </is>
       </c>
       <c r="D135" s="3" t="n">
@@ -10125,17 +10125,17 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>肢体无力</t>
+          <t>眼红</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有过敏或戴隐形眼镜？</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
@@ -10145,17 +10145,17 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>肢体无力</t>
+          <t>视力下降</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>onset</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>视力下降是突然还是逐渐？</t>
         </is>
       </c>
       <c r="D137" s="3" t="n">
@@ -10165,17 +10165,17 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>肢体无力</t>
+          <t>视力下降</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>单眼还是双眼？</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
@@ -10185,17 +10185,17 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>肢体无力</t>
+          <t>视力下降</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>有没有眼痛、视野缺损、黑影？</t>
         </is>
       </c>
       <c r="D139" s="3" t="n">
@@ -10205,17 +10205,17 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>肢体无力</t>
+          <t>视力下降</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>和用眼、外伤有关吗？</t>
         </is>
       </c>
       <c r="D140" s="3" t="n">
@@ -10225,17 +10225,17 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>肢体无力</t>
+          <t>视力下降</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有糖尿病、高血压？</t>
         </is>
       </c>
       <c r="D141" s="3" t="n">
@@ -10245,17 +10245,17 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>麻木</t>
+          <t>失眠</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>是入睡困难、易醒还是早醒？</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
@@ -10265,7 +10265,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>麻木</t>
+          <t>失眠</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>失眠多久了？</t>
         </is>
       </c>
       <c r="D143" s="3" t="n">
@@ -10285,17 +10285,17 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>麻木</t>
+          <t>失眠</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>有没有精神压力或作息变化？</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
@@ -10305,17 +10305,17 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>麻木</t>
+          <t>失眠</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>有没有焦虑、情绪低落？</t>
         </is>
       </c>
       <c r="D145" s="3" t="n">
@@ -10325,17 +10325,17 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>麻木</t>
+          <t>失眠</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有用药或咖啡因摄入？</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
@@ -10345,17 +10345,17 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>麻木</t>
+          <t>焦虑</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>焦虑多久了？</t>
         </is>
       </c>
       <c r="D147" s="3" t="n">
@@ -10365,17 +10365,17 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>麻木</t>
+          <t>焦虑</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>什么情况下加重？</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
@@ -10385,17 +10385,17 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>麻木</t>
+          <t>焦虑</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>有没有心慌、多汗、坐立不安？</t>
         </is>
       </c>
       <c r="D149" s="3" t="n">
@@ -10405,17 +10405,17 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>麻木</t>
+          <t>焦虑</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>severity</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>是否影响工作生活？</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
@@ -10425,17 +10425,17 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>麻木</t>
+          <t>焦虑</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有类似发作或家族史？</t>
         </is>
       </c>
       <c r="D151" s="3" t="n">
@@ -10445,17 +10445,17 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>尿频</t>
+          <t>乏力</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>乏力多久了？</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
@@ -10465,17 +10465,17 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>尿频</t>
+          <t>乏力</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>休息后能缓解吗？</t>
         </is>
       </c>
       <c r="D153" s="3" t="n">
@@ -10485,17 +10485,17 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>尿频</t>
+          <t>乏力</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>有没有消瘦、发热、纳差？</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
@@ -10505,7 +10505,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>尿频</t>
+          <t>乏力</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -10515,7 +10515,7 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>是否影响日常活动？</t>
         </is>
       </c>
       <c r="D155" s="3" t="n">
@@ -10525,17 +10525,17 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>尿频</t>
+          <t>乏力</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有慢性病或用药？</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
@@ -10545,17 +10545,17 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>尿频</t>
+          <t>消瘦</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>体重下降多久了？</t>
         </is>
       </c>
       <c r="D157" s="3" t="n">
@@ -10565,17 +10565,17 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>尿频</t>
+          <t>消瘦</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>下降了多少斤？</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
@@ -10585,17 +10585,17 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>尿频</t>
+          <t>消瘦</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>有没有食欲亢进、多饮多尿、腹泻？</t>
         </is>
       </c>
       <c r="D159" s="3" t="n">
@@ -10605,17 +10605,17 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>尿频</t>
+          <t>消瘦</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>有没有刻意节食或运动？</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
@@ -10625,17 +10625,17 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>尿频</t>
+          <t>消瘦</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有糖尿病、甲亢、肿瘤史？</t>
         </is>
       </c>
       <c r="D161" s="3" t="n">
@@ -10645,7 +10645,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>尿痛</t>
+          <t>水肿</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>水肿在哪个部位？</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
@@ -10665,7 +10665,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>尿痛</t>
+          <t>水肿</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>水肿多久了？</t>
         </is>
       </c>
       <c r="D163" s="3" t="n">
@@ -10685,7 +10685,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>尿痛</t>
+          <t>水肿</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>是凹陷性还是非凹陷性？</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
@@ -10705,17 +10705,17 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>尿痛</t>
+          <t>水肿</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>有没有气短、尿少、泡沫尿？</t>
         </is>
       </c>
       <c r="D165" s="3" t="n">
@@ -10725,17 +10725,17 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>尿痛</t>
+          <t>水肿</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有心肝肾疾病？</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
@@ -10745,17 +10745,17 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>尿痛</t>
+          <t>便血</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>血是鲜红还是暗红？附在大便表面还是混在里？</t>
         </is>
       </c>
       <c r="D167" s="3" t="n">
@@ -10765,17 +10765,17 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>尿痛</t>
+          <t>便血</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>便血多久了？</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
@@ -10785,17 +10785,17 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>尿痛</t>
+          <t>便血</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>量大不大？</t>
         </is>
       </c>
       <c r="D169" s="3" t="n">
@@ -10805,17 +10805,17 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>尿痛</t>
+          <t>便血</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>有没有腹痛、排便习惯改变？</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
@@ -10825,17 +10825,17 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>尿痛</t>
+          <t>便血</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有痔疮或肠病家族史？</t>
         </is>
       </c>
       <c r="D171" s="3" t="n">
@@ -10845,17 +10845,17 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>血尿</t>
+          <t>便秘</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>便秘多久了？</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
@@ -10865,17 +10865,17 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>血尿</t>
+          <t>便秘</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>frequency</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>几天一次？</t>
         </is>
       </c>
       <c r="D173" s="3" t="n">
@@ -10885,7 +10885,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>血尿</t>
+          <t>便秘</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>大便干硬吗？排便费力吗？</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
@@ -10905,17 +10905,17 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>血尿</t>
+          <t>便秘</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>有没有腹胀、腹痛、便血？</t>
         </is>
       </c>
       <c r="D175" s="3" t="n">
@@ -10925,17 +10925,17 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>血尿</t>
+          <t>便秘</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有用药或饮水少？</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
@@ -10945,17 +10945,17 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>血尿</t>
+          <t>腹胀</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>腹胀多久了？</t>
         </is>
       </c>
       <c r="D177" s="3" t="n">
@@ -10965,17 +10965,17 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>血尿</t>
+          <t>腹胀</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>和进食有关吗？</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
@@ -10985,17 +10985,17 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>血尿</t>
+          <t>腹胀</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>有没有腹痛、排气减少、呕吐？</t>
         </is>
       </c>
       <c r="D179" s="3" t="n">
@@ -11005,17 +11005,17 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>血尿</t>
+          <t>腹胀</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>是持续还是阵发？</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
@@ -11025,17 +11025,17 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>血尿</t>
+          <t>腹胀</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有胃肠疾病？</t>
         </is>
       </c>
       <c r="D181" s="3" t="n">
@@ -11045,17 +11045,17 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>腰痛</t>
+          <t>气短</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>气短什么情况下出现（活动/休息/夜间）？</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
@@ -11065,17 +11065,17 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>腰痛</t>
+          <t>气短</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>severity</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>能走多远或上几层楼？</t>
         </is>
       </c>
       <c r="D183" s="3" t="n">
@@ -11085,17 +11085,17 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>腰痛</t>
+          <t>气短</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>有没有咳嗽、胸痛、心悸？</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
@@ -11105,17 +11105,17 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>腰痛</t>
+          <t>气短</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>多久了？</t>
         </is>
       </c>
       <c r="D185" s="3" t="n">
@@ -11125,17 +11125,17 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>腰痛</t>
+          <t>气短</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有心肺疾病？</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
@@ -11145,17 +11145,17 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>腰痛</t>
+          <t>背痛</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>背痛在哪个部位？</t>
         </is>
       </c>
       <c r="D187" s="3" t="n">
@@ -11165,17 +11165,17 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>腰痛</t>
+          <t>背痛</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>是酸痛、刺痛还是放射痛？</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
@@ -11185,17 +11185,17 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>腰痛</t>
+          <t>背痛</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>什么姿势加重？</t>
         </is>
       </c>
       <c r="D189" s="3" t="n">
@@ -11205,17 +11205,17 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>腰痛</t>
+          <t>背痛</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>有没有下肢麻木、无力？</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
@@ -11225,17 +11225,17 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>腰痛</t>
+          <t>背痛</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有外伤或久坐？</t>
         </is>
       </c>
       <c r="D191" s="3" t="n">
@@ -11245,17 +11245,17 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>关节痛</t>
+          <t>颈痛</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>颈痛多久了？</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
@@ -11265,17 +11265,17 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>关节痛</t>
+          <t>颈痛</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>是酸痛、僵硬还是放射痛？</t>
         </is>
       </c>
       <c r="D193" s="3" t="n">
@@ -11285,17 +11285,17 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>关节痛</t>
+          <t>颈痛</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>转头或低头时加重吗？</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
@@ -11305,17 +11305,17 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>关节痛</t>
+          <t>颈痛</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>有没有上肢麻木、头晕？</t>
         </is>
       </c>
       <c r="D195" s="3" t="n">
@@ -11325,17 +11325,17 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>关节痛</t>
+          <t>颈痛</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有久坐或外伤？</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
@@ -11345,17 +11345,17 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>关节痛</t>
+          <t>牙痛</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>哪颗牙痛？上牙还是下牙？</t>
         </is>
       </c>
       <c r="D197" s="3" t="n">
@@ -11365,17 +11365,17 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>关节痛</t>
+          <t>牙痛</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>是持续痛、冷热痛还是咬合痛？</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
@@ -11385,17 +11385,17 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>关节痛</t>
+          <t>牙痛</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>痛了多久？夜间加重吗？</t>
         </is>
       </c>
       <c r="D199" s="3" t="n">
@@ -11405,17 +11405,17 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>关节痛</t>
+          <t>牙痛</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>冷热刺激时痛吗？</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
@@ -11425,17 +11425,17 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>关节痛</t>
+          <t>牙痛</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有龋齿或牙周病？</t>
         </is>
       </c>
       <c r="D201" s="3" t="n">
@@ -11445,7 +11445,7 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>皮疹</t>
+          <t>耳痛</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>哪只耳朵痛？</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
@@ -11465,7 +11465,7 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>皮疹</t>
+          <t>耳痛</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>痛了多久？</t>
         </is>
       </c>
       <c r="D203" s="3" t="n">
@@ -11485,17 +11485,17 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>皮疹</t>
+          <t>耳痛</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>有没有听力下降、耳鸣、流脓？</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
@@ -11505,17 +11505,17 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>皮疹</t>
+          <t>耳痛</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>有没有感冒、游泳进水？</t>
         </is>
       </c>
       <c r="D205" s="3" t="n">
@@ -11525,17 +11525,17 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>皮疹</t>
+          <t>耳痛</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有中耳炎史？</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
@@ -11545,17 +11545,17 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>皮疹</t>
+          <t>月经不调</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>周期怎么乱（提前/推迟/不规律）？</t>
         </is>
       </c>
       <c r="D207" s="3" t="n">
@@ -11565,17 +11565,17 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>皮疹</t>
+          <t>月经不调</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>持续多久了？</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -11585,17 +11585,17 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>皮疹</t>
+          <t>月经不调</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>经量多还是少？</t>
         </is>
       </c>
       <c r="D209" s="3" t="n">
@@ -11605,17 +11605,17 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>皮疹</t>
+          <t>月经不调</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>有没有痛经、白带异常？</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
@@ -11625,17 +11625,17 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>皮疹</t>
+          <t>月经不调</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有精神压力或体重变化？</t>
         </is>
       </c>
       <c r="D211" s="3" t="n">
@@ -11645,17 +11645,17 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>瘙痒</t>
+          <t>白带异常</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>白带是什么颜色、气味、性状？</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
@@ -11665,7 +11665,7 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>瘙痒</t>
+          <t>白带异常</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -11685,17 +11685,17 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>瘙痒</t>
+          <t>白带异常</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>有没有外阴瘙痒、灼痛？</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
@@ -11705,17 +11705,17 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>瘙痒</t>
+          <t>白带异常</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>和月经周期有关吗？</t>
         </is>
       </c>
       <c r="D215" s="3" t="n">
@@ -11725,17 +11725,17 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>瘙痒</t>
+          <t>白带异常</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有阴道炎史？</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
@@ -11745,17 +11745,17 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>瘙痒</t>
+          <t>停经</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>停经多久了？</t>
         </is>
       </c>
       <c r="D217" s="3" t="n">
@@ -11765,17 +11765,17 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>瘙痒</t>
+          <t>停经</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>possibility</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>有没有性生活？可能怀孕吗？</t>
         </is>
       </c>
       <c r="D218" s="3" t="n">
@@ -11785,17 +11785,17 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>瘙痒</t>
+          <t>停经</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>有没有恶心、乳房胀痛？</t>
         </is>
       </c>
       <c r="D219" s="3" t="n">
@@ -11805,17 +11805,17 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>瘙痒</t>
+          <t>停经</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>以前月经规律吗？</t>
         </is>
       </c>
       <c r="D220" s="3" t="n">
@@ -11825,17 +11825,17 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>瘙痒</t>
+          <t>停经</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有精神压力或体重骤变？</t>
         </is>
       </c>
       <c r="D221" s="3" t="n">
@@ -11845,7 +11845,7 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>咽痛</t>
+          <t>皮肤瘙痒</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>哪里痒？范围多大？</t>
         </is>
       </c>
       <c r="D222" s="3" t="n">
@@ -11865,7 +11865,7 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>咽痛</t>
+          <t>皮肤瘙痒</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>痒了多久？</t>
         </is>
       </c>
       <c r="D223" s="3" t="n">
@@ -11885,17 +11885,17 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>咽痛</t>
+          <t>皮肤瘙痒</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>什么情况下加重？</t>
         </is>
       </c>
       <c r="D224" s="3" t="n">
@@ -11905,17 +11905,17 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>咽痛</t>
+          <t>皮肤瘙痒</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>有没有皮疹、干燥、黄疸？</t>
         </is>
       </c>
       <c r="D225" s="3" t="n">
@@ -11925,17 +11925,17 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>咽痛</t>
+          <t>皮肤瘙痒</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有过敏或肝胆疾病？</t>
         </is>
       </c>
       <c r="D226" s="3" t="n">
@@ -11945,17 +11945,17 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>咽痛</t>
+          <t>脱发</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>是斑片状还是整体稀疏？</t>
         </is>
       </c>
       <c r="D227" s="3" t="n">
@@ -11965,17 +11965,17 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>咽痛</t>
+          <t>脱发</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>脱发多久了？</t>
         </is>
       </c>
       <c r="D228" s="3" t="n">
@@ -11985,17 +11985,17 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>咽痛</t>
+          <t>脱发</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>每天掉多少？</t>
         </is>
       </c>
       <c r="D229" s="3" t="n">
@@ -12005,17 +12005,17 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>咽痛</t>
+          <t>脱发</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>有没有头皮痒、红斑？</t>
         </is>
       </c>
       <c r="D230" s="3" t="n">
@@ -12025,17 +12025,17 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>咽痛</t>
+          <t>脱发</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有精神压力、用药、家族史？</t>
         </is>
       </c>
       <c r="D231" s="3" t="n">
@@ -12045,17 +12045,17 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>鼻塞</t>
+          <t>口干</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>口干多久了？</t>
         </is>
       </c>
       <c r="D232" s="3" t="n">
@@ -12065,17 +12065,17 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>鼻塞</t>
+          <t>口干</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>喝水能缓解吗？</t>
         </is>
       </c>
       <c r="D233" s="3" t="n">
@@ -12085,17 +12085,17 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>鼻塞</t>
+          <t>口干</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>有没有眼干、多饮多尿？</t>
         </is>
       </c>
       <c r="D234" s="3" t="n">
@@ -12105,7 +12105,7 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>鼻塞</t>
+          <t>口干</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>是否影响进食吞咽？</t>
         </is>
       </c>
       <c r="D235" s="3" t="n">
@@ -12125,17 +12125,17 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>鼻塞</t>
+          <t>口干</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有糖尿病或干燥综合征？</t>
         </is>
       </c>
       <c r="D236" s="3" t="n">
@@ -12145,17 +12145,17 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>鼻塞</t>
+          <t>多饮</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>多饮多久了？</t>
         </is>
       </c>
       <c r="D237" s="3" t="n">
@@ -12165,17 +12165,17 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>鼻塞</t>
+          <t>多饮</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>每天喝多少水？</t>
         </is>
       </c>
       <c r="D238" s="3" t="n">
@@ -12185,17 +12185,17 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>鼻塞</t>
+          <t>多饮</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>有没有多尿、消瘦、乏力？</t>
         </is>
       </c>
       <c r="D239" s="3" t="n">
@@ -12205,17 +12205,17 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>鼻塞</t>
+          <t>多饮</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>和天气、运动有关吗？</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
@@ -12225,17 +12225,17 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>鼻塞</t>
+          <t>多饮</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有糖尿病史？</t>
         </is>
       </c>
       <c r="D241" s="3" t="n">
@@ -12245,17 +12245,17 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>耳鸣</t>
+          <t>多尿</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>frequency</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>具体在哪个部位？</t>
+          <t>一天尿几次？夜尿几次？</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">
@@ -12265,7 +12265,7 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>耳鸣</t>
+          <t>多尿</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>出现多久了？</t>
+          <t>多尿多久了？</t>
         </is>
       </c>
       <c r="D243" s="3" t="n">
@@ -12285,17 +12285,17 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>耳鸣</t>
+          <t>多尿</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>是什么样的感觉（性质）？</t>
+          <t>尿量多吗？</t>
         </is>
       </c>
       <c r="D244" s="3" t="n">
@@ -12305,17 +12305,17 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>耳鸣</t>
+          <t>多尿</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>严重程度如何（轻/中/重）？</t>
+          <t>有没有多饮、消瘦、乏力？</t>
         </is>
       </c>
       <c r="D245" s="3" t="n">
@@ -12325,17 +12325,17 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>耳鸣</t>
+          <t>多尿</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>什么情况下加重或缓解？</t>
+          <t>有没有糖尿病或尿崩症？</t>
         </is>
       </c>
       <c r="D246" s="3" t="n">
@@ -12345,17 +12345,17 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>耳鸣</t>
+          <t>体重下降</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>accompanying</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>有没有其它伴随症状？</t>
+          <t>下降了多少？</t>
         </is>
       </c>
       <c r="D247" s="3" t="n">
@@ -12365,17 +12365,17 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>耳鸣</t>
+          <t>体重下降</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>以前有没有类似情况或相关病史？</t>
+          <t>多久内下降的？</t>
         </is>
       </c>
       <c r="D248" s="3" t="n">
@@ -12385,17 +12385,17 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>耳鸣</t>
+          <t>体重下降</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>accompanying</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>目前有没有在用药？</t>
+          <t>有没有食欲亢进、多饮多尿、腹泻？</t>
         </is>
       </c>
       <c r="D249" s="3" t="n">
@@ -12405,17 +12405,17 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>耳鸣</t>
+          <t>体重下降</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>有没有发热？体温多少？</t>
+          <t>有没有刻意节食？</t>
         </is>
       </c>
       <c r="D250" s="3" t="n">
@@ -12425,17 +12425,17 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>耳鸣</t>
+          <t>体重下降</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>疼痛有没有向其它部位放射？</t>
+          <t>有没有糖尿病、甲亢、肿瘤史？</t>
         </is>
       </c>
       <c r="D251" s="3" t="n">

--- a/kb/医学知识库源数据.xlsx
+++ b/kb/医学知识库源数据.xlsx
@@ -27382,12 +27382,12 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
+          <t>疾病名称</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
           <t>科室编码</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>疾病名称</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
